--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121221122</v>
+        <v>121222359</v>
       </c>
       <c r="B2" t="n">
-        <v>97025</v>
+        <v>8432</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508583</v>
+        <v>508756</v>
       </c>
       <c r="R2" t="n">
-        <v>6513044</v>
+        <v>6513314</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222359</v>
+        <v>121220935</v>
       </c>
       <c r="B3" t="n">
-        <v>8432</v>
+        <v>90717</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +794,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508756</v>
+        <v>508616</v>
       </c>
       <c r="R3" t="n">
-        <v>6513314</v>
+        <v>6513022</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,12 +872,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -887,7 +887,7 @@
         <v>121222441</v>
       </c>
       <c r="B4" t="n">
-        <v>97025</v>
+        <v>97035</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121220935</v>
+        <v>121221122</v>
       </c>
       <c r="B5" t="n">
-        <v>90707</v>
+        <v>97035</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508616</v>
+        <v>508583</v>
       </c>
       <c r="R5" t="n">
-        <v>6513022</v>
+        <v>6513044</v>
       </c>
       <c r="S5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,12 +1076,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222359</v>
+        <v>121220935</v>
       </c>
       <c r="B2" t="n">
-        <v>8432</v>
+        <v>90717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,46 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508756</v>
+        <v>508616</v>
       </c>
       <c r="R2" t="n">
-        <v>6513314</v>
+        <v>6513022</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -770,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121220935</v>
+        <v>121221122</v>
       </c>
       <c r="B3" t="n">
-        <v>90717</v>
+        <v>97035</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508616</v>
+        <v>508583</v>
       </c>
       <c r="R3" t="n">
-        <v>6513022</v>
+        <v>6513044</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222441</v>
+        <v>121222359</v>
       </c>
       <c r="B4" t="n">
-        <v>97035</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508780</v>
+        <v>508756</v>
       </c>
       <c r="R4" t="n">
-        <v>6513359</v>
+        <v>6513314</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121221122</v>
+        <v>121222441</v>
       </c>
       <c r="B5" t="n">
         <v>97035</v>
@@ -1022,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508583</v>
+        <v>508780</v>
       </c>
       <c r="R5" t="n">
-        <v>6513044</v>
+        <v>6513359</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121220935</v>
       </c>
       <c r="B2" t="n">
-        <v>90717</v>
+        <v>90729</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121221122</v>
+        <v>121222441</v>
       </c>
       <c r="B3" t="n">
-        <v>97035</v>
+        <v>97048</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508583</v>
+        <v>508780</v>
       </c>
       <c r="R3" t="n">
-        <v>6513044</v>
+        <v>6513359</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222359</v>
+        <v>121221122</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>97048</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,42 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508756</v>
+        <v>508583</v>
       </c>
       <c r="R4" t="n">
-        <v>6513314</v>
+        <v>6513044</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222441</v>
+        <v>121222359</v>
       </c>
       <c r="B5" t="n">
-        <v>97035</v>
+        <v>8432</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508780</v>
+        <v>508756</v>
       </c>
       <c r="R5" t="n">
-        <v>6513359</v>
+        <v>6513314</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121220935</v>
+        <v>121221122</v>
       </c>
       <c r="B2" t="n">
-        <v>90729</v>
+        <v>97049</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508616</v>
+        <v>508583</v>
       </c>
       <c r="R2" t="n">
-        <v>6513022</v>
+        <v>6513044</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222441</v>
+        <v>121220935</v>
       </c>
       <c r="B3" t="n">
-        <v>97048</v>
+        <v>90730</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508780</v>
+        <v>508616</v>
       </c>
       <c r="R3" t="n">
-        <v>6513359</v>
+        <v>6513022</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121221122</v>
+        <v>121222359</v>
       </c>
       <c r="B4" t="n">
-        <v>97048</v>
+        <v>8432</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,37 +895,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508583</v>
+        <v>508756</v>
       </c>
       <c r="R4" t="n">
-        <v>6513044</v>
+        <v>6513314</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222359</v>
+        <v>121222441</v>
       </c>
       <c r="B5" t="n">
-        <v>8432</v>
+        <v>97049</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508756</v>
+        <v>508780</v>
       </c>
       <c r="R5" t="n">
-        <v>6513314</v>
+        <v>6513359</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121221122</v>
       </c>
       <c r="B2" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121220935</v>
+        <v>121222359</v>
       </c>
       <c r="B3" t="n">
-        <v>90730</v>
+        <v>8435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,41 +789,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508616</v>
+        <v>508756</v>
       </c>
       <c r="R3" t="n">
-        <v>6513022</v>
+        <v>6513314</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +872,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222359</v>
+        <v>121220935</v>
       </c>
       <c r="B4" t="n">
-        <v>8432</v>
+        <v>90733</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508756</v>
+        <v>508616</v>
       </c>
       <c r="R4" t="n">
-        <v>6513314</v>
+        <v>6513022</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -989,7 +989,7 @@
         <v>121222441</v>
       </c>
       <c r="B5" t="n">
-        <v>97049</v>
+        <v>97052</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121221122</v>
+        <v>121222441</v>
       </c>
       <c r="B2" t="n">
         <v>97052</v>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508583</v>
+        <v>508780</v>
       </c>
       <c r="R2" t="n">
-        <v>6513044</v>
+        <v>6513359</v>
       </c>
       <c r="S2" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121222359</v>
+        <v>121220935</v>
       </c>
       <c r="B3" t="n">
-        <v>8435</v>
+        <v>90733</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,46 +789,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508756</v>
+        <v>508616</v>
       </c>
       <c r="R3" t="n">
-        <v>6513314</v>
+        <v>6513022</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121220935</v>
+        <v>121222359</v>
       </c>
       <c r="B4" t="n">
-        <v>90733</v>
+        <v>8435</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +891,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508616</v>
+        <v>508756</v>
       </c>
       <c r="R4" t="n">
-        <v>6513022</v>
+        <v>6513314</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222441</v>
+        <v>121221122</v>
       </c>
       <c r="B5" t="n">
         <v>97052</v>
@@ -1022,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508780</v>
+        <v>508583</v>
       </c>
       <c r="R5" t="n">
-        <v>6513359</v>
+        <v>6513044</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121222441</v>
       </c>
       <c r="B2" t="n">
-        <v>97052</v>
+        <v>97058</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121220935</v>
+        <v>121221122</v>
       </c>
       <c r="B3" t="n">
-        <v>90733</v>
+        <v>97058</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508616</v>
+        <v>508583</v>
       </c>
       <c r="R3" t="n">
-        <v>6513022</v>
+        <v>6513044</v>
       </c>
       <c r="S3" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222359</v>
+        <v>121220935</v>
       </c>
       <c r="B4" t="n">
-        <v>8435</v>
+        <v>90739</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,46 +891,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508756</v>
+        <v>508616</v>
       </c>
       <c r="R4" t="n">
-        <v>6513314</v>
+        <v>6513022</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,22 +969,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121221122</v>
+        <v>121222359</v>
       </c>
       <c r="B5" t="n">
-        <v>97052</v>
+        <v>8435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,37 +997,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508583</v>
+        <v>508756</v>
       </c>
       <c r="R5" t="n">
-        <v>6513044</v>
+        <v>6513314</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222441</v>
+        <v>121220935</v>
       </c>
       <c r="B2" t="n">
-        <v>97058</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508780</v>
+        <v>508616</v>
       </c>
       <c r="R2" t="n">
-        <v>6513359</v>
+        <v>6513022</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,22 +765,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121221122</v>
+        <v>121222359</v>
       </c>
       <c r="B3" t="n">
-        <v>97058</v>
+        <v>8435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>508583</v>
+        <v>508756</v>
       </c>
       <c r="R3" t="n">
-        <v>6513044</v>
+        <v>6513314</v>
       </c>
       <c r="S3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121220935</v>
+        <v>121222441</v>
       </c>
       <c r="B4" t="n">
-        <v>90739</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,41 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508616</v>
+        <v>508780</v>
       </c>
       <c r="R4" t="n">
-        <v>6513022</v>
+        <v>6513359</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +974,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121222359</v>
+        <v>121221122</v>
       </c>
       <c r="B5" t="n">
-        <v>8435</v>
+        <v>97059</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,42 +1002,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508756</v>
+        <v>508583</v>
       </c>
       <c r="R5" t="n">
-        <v>6513314</v>
+        <v>6513044</v>
       </c>
       <c r="S5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121220935</v>
+        <v>121222441</v>
       </c>
       <c r="B2" t="n">
-        <v>90740</v>
+        <v>97059</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508616</v>
+        <v>508780</v>
       </c>
       <c r="R2" t="n">
-        <v>6513022</v>
+        <v>6513359</v>
       </c>
       <c r="S2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121222441</v>
+        <v>121220935</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>90740</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,41 +896,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508780</v>
+        <v>508616</v>
       </c>
       <c r="R4" t="n">
-        <v>6513359</v>
+        <v>6513022</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +974,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121222441</v>
+        <v>121220935</v>
       </c>
       <c r="B2" t="n">
-        <v>97059</v>
+        <v>90740</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogslund, Skogslund, Ög</t>
+          <t>Backen, Backen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>508780</v>
+        <v>508616</v>
       </c>
       <c r="R2" t="n">
-        <v>6513359</v>
+        <v>6513022</v>
       </c>
       <c r="S2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -765,12 +765,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Carina Faxén</t>
+          <t>Eva Siljeholm</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121220935</v>
+        <v>121221122</v>
       </c>
       <c r="B4" t="n">
-        <v>90740</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,13 +924,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>508616</v>
+        <v>508583</v>
       </c>
       <c r="R4" t="n">
-        <v>6513022</v>
+        <v>6513044</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,19 +974,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Eva Siljeholm</t>
+          <t>Carina Faxén</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121221122</v>
+        <v>121222441</v>
       </c>
       <c r="B5" t="n">
         <v>97059</v>
@@ -1022,17 +1022,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Backen, Backen, Ög</t>
+          <t>Skogslund, Skogslund, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>508583</v>
+        <v>508780</v>
       </c>
       <c r="R5" t="n">
-        <v>6513044</v>
+        <v>6513359</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 49690-2024 artfynd.xlsx
+++ b/artfynd/A 49690-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>121220935</v>
       </c>
       <c r="B2" t="n">
-        <v>90740</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>121222359</v>
       </c>
       <c r="B3" t="n">
-        <v>8435</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,12 +877,7 @@
         <v>121221122</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,12 +974,7 @@
         <v>121222441</v>
       </c>
       <c r="B5" t="n">
-        <v>97059</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
